--- a/docs/kamikami-sewer-tariff/階上町下水道使用料改定_試算エビデンス.xlsx
+++ b/docs/kamikami-sewer-tariff/階上町下水道使用料改定_試算エビデンス.xlsx
@@ -9955,7 +9955,7 @@
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
   </cols>
@@ -9984,7 +9984,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>いずれの補正も改定率（+9.93%）および条例用税抜単価（1,008/73/190/220円）には影響しない</t>
+          <t>いずれの補正も条例用税抜単価には影響しない。単価はその後の精査でB案 1,008/73/191/220円（平均増収率+10.05%）に確定している</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>平年度増収額 中心案(税込・円)</t>
+          <t>平年度増収額 B案(税込・円)</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -10276,19 +10276,19 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>中心案適用後（R8予算×1.0993）</t>
+          <t>B案適用後（R8予算×1.1005）</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr"/>
       <c r="D20" s="11" t="n">
-        <v>46067000</v>
+        <v>46117000</v>
       </c>
       <c r="E20" s="9" t="inlineStr"/>
       <c r="F20" s="9" t="inlineStr"/>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>増収 約+4,161千円</t>
+          <t>増収 約+4,211千円（税込）／+3,829千円（税抜）</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12185,7 @@
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>改定後(+9.93%)</t>
+          <t>改定後(+10.05%・B案)</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -12431,13 +12431,13 @@
         <v>41906</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>46067</v>
+        <v>46117</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>4161</v>
+        <v>4211</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>3783</v>
+        <v>3829</v>
       </c>
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr">
@@ -12453,16 +12453,16 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>44579</v>
+        <v>44568</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>49005</v>
+        <v>49047</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>4427</v>
+        <v>4479</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>4024</v>
+        <v>4072</v>
       </c>
       <c r="F15" s="9" t="inlineStr"/>
       <c r="G15" s="9" t="inlineStr">
@@ -12481,13 +12481,13 @@
         <v>44645</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>49078</v>
+        <v>49132</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>4433</v>
+        <v>4487</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>4030</v>
+        <v>4079</v>
       </c>
       <c r="F16" s="9" t="inlineStr"/>
       <c r="G16" s="9" t="inlineStr">
@@ -12513,11 +12513,11 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>中心案適用後（R7年間全件調定ベース）</t>
+          <t>B案適用後（R7年間全件調定ベース）</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>49005</v>
+        <v>49047</v>
       </c>
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="9" t="inlineStr"/>
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>-3268</v>
+        <v>-3226</v>
       </c>
       <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="9" t="inlineStr"/>
@@ -12624,12 +12624,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>中心案適用後（税抜44,617千円）</t>
+          <t>B案適用後（税抜44,665千円）</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr"/>
@@ -12638,7 +12638,7 @@
       <c r="F26" s="9" t="inlineStr"/>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>+4.9ポイント</t>
+          <t>+5.0ポイント</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>54.4%（+4.9ﾎﾟｲﾝﾄ）</t>
+          <t>54.5%（+5.0ﾎﾟｲﾝﾄ）</t>
         </is>
       </c>
     </row>
@@ -12982,17 +12982,17 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>（参考）使用料を税込のまま算定した場合の経費回収率</t>
+          <t>（参考）使用料を税込のまま算定した場合のR7経費回収率</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.45%</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>5.0ﾎﾟｲﾝﾄ過大となる</t>
+          <t>税抜49.5%に対し4.95ﾎﾟｲﾝﾄ過大となる</t>
         </is>
       </c>
     </row>

--- a/docs/kamikami-sewer-tariff/階上町下水道使用料改定_試算エビデンス.xlsx
+++ b/docs/kamikami-sewer-tariff/階上町下水道使用料改定_試算エビデンス.xlsx
@@ -42,6 +42,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_料金収入算定の精査" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_条例との整合確認" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_一律改定との比較" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_基本使用料の改定" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_料金区分の変更" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_基本水量の感度" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -964,7 +967,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>★説明資料 表12・表14の根拠。作成要領による各表の税区分と経営指標への反映</t>
+          <t>★説明資料 表16・表19の根拠。作成要領による各表の税区分と経営指標への反映</t>
         </is>
       </c>
     </row>
@@ -988,7 +991,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>★説明資料 表15の根拠。条例別表・第17条・第18条との機械的な整合確認</t>
+          <t>★説明資料 表22の根拠。条例別表・第17条・第18条との機械的な整合確認</t>
         </is>
       </c>
     </row>
@@ -1005,42 +1008,54 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>35_基本使用料の改定</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>★説明資料 表13・表14の根拠。基本使用料を動かした場合の増収と負担配分</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>経費回収率の定義</t>
+          <t>36_料金区分の変更</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>使用料収入 ÷ 汚水処理費。汚水処理費は32表の維持管理費（汚水分）のみ</t>
+          <t>★説明資料 表15・表16の根拠。区分数・境界水量・基本水量を変えた7案の比較</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>37_基本水量の感度</t>
+        </is>
+      </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>資本費（減価償却費−長期前受金戻入＋支払利息）は全額が「分流式下水道等に要する経費」</t>
+          <t>★基本水量を下げる場合、基本水量内1,934レコードの想定水量による幅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>として基準内繰入金で措置されるため、汚水処理費には含まれない</t>
-        </is>
-      </c>
+      <c r="B46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>経費回収率の定義</t>
+        </is>
+      </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>R6実績：公共 33,652÷67,464＝49.9%／漁集 7,229÷19,614＝36.9%</t>
+          <t>使用料収入 ÷ 汚水処理費。汚水処理費は32表の維持管理費（汚水分）のみ</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1063,23 @@
       <c r="A48" s="3" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>※水洗便所等普及費330千円（漁集は不明水処理費2,318千円）は現行額が継続する前提</t>
+          <t>資本費（減価償却費−長期前受金戻入＋支払利息）は全額が「分流式下水道等に要する経費」</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>として基準内繰入金で措置されるため、汚水処理費には含まれない</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>説明資料との対応</t>
-        </is>
-      </c>
+      <c r="A50" s="3" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>シート20〜24が「下水道使用料の改定について（6〜10㎥区分の是正を含む</t>
+          <t>R6実績：公共 33,652÷67,464＝49.9%／漁集 7,229÷19,614＝36.9%</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1087,7 @@
       <c r="A51" s="3" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>料金体系の見直し案）」の各表・各図の根拠にあたる</t>
+          <t>※水洗便所等普及費330千円（漁集は不明水処理費2,318千円）は現行額が継続する前提</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1098,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>6〜10㎥の単価差とは</t>
+          <t>説明資料との対応</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>現行の6〜10㎥は税抜37円で、11〜50㎥（税抜174円）の4.7分の1しかない</t>
+          <t>シート20〜24が「下水道使用料の改定について（6〜10㎥区分の是正を含む</t>
         </is>
       </c>
     </row>
@@ -1096,23 +1111,23 @@
       <c r="A54" s="3" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>公共下水道では従量課金対象水量の37.9%にこの単価が適用される一方、従量収入は5.3%</t>
+          <t>料金体系の見直し案）」の各表・各図の根拠にあたる</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>※従量課金対象水量＝基本使用料に含まれる水量（2か月10㎥）を除いた水量。全汚水量ではない</t>
-        </is>
-      </c>
+      <c r="B55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>6〜10㎥の単価差とは</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>税抜174円に揃えると平年度で8,493,858円（現行比 約+19.8%）の増収余地がある</t>
+          <t>現行の6〜10㎥は税抜37円で、11〜50㎥（税抜174円）の4.7分の1しかない</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1135,7 @@
       <c r="A57" s="3" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ただし揃えると11〜50㎥が6〜10㎥を下回る逆転体系となり、月10㎥世帯は+57.4%となる</t>
+          <t>公共下水道では従量課金対象水量の37.9%にこの単価が適用される一方、従量収入は5.3%</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1143,7 @@
       <c r="A58" s="3" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>中心案は「基本使用料1,008円据置・6〜10㎥を税抜73円」（単価差縮小率26.3%）</t>
+          <t>※従量課金対象水量＝基本使用料に含まれる水量（2か月10㎥）を除いた水量。全汚水量ではない</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1151,23 @@
       <c r="A59" s="3" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>調定額ベースの平均増収率は約9.9%だが、6〜10㎥の単価自体は+97.3%</t>
+          <t>税抜174円に揃えると平年度で8,493,858円（現行比 約+19.8%）の増収余地がある</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ただし揃えると11〜50㎥が6〜10㎥を下回る逆転体系となり、月10㎥世帯は+57.4%となる</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>料金は税抜で設計</t>
-        </is>
-      </c>
+      <c r="A61" s="3" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>条例別表は税抜のため、料金案も税抜の整数単価で設計している</t>
+          <t>中心案は「基本使用料1,008円据置・6〜10㎥を税抜73円」（単価差縮小率26.3%）</t>
         </is>
       </c>
     </row>
@@ -1160,31 +1175,31 @@
       <c r="A62" s="3" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>税込は条例により税抜額に消費税を加算し、1円未満を切り捨てて算定</t>
+          <t>調定額ベースの平均増収率は約9.9%だが、6〜10㎥の単価自体は+97.3%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>改正対象は公共下水道条例・漁業集落排水処理施設条例の2条例</t>
-        </is>
-      </c>
+      <c r="B63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr"/>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>料金は税抜で設計</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>条例別表は税抜のため、料金案も税抜の整数単価で設計している</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>増収額は平年度ベース</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>施行日が未定のため初年度影響額は含まない。確定後に別途算定が必要</t>
+          <t>税込は条例により税抜額に消費税を加算し、1円未満を切り捨てて算定</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1207,7 @@
       <c r="A66" s="3" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>経費回収率はR6決算の使用料・汚水処理費を固定した静態試算の参考値</t>
+          <t>改正対象は公共下水道条例・漁業集落排水処理施設条例の2条例</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1218,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>検討する改定率</t>
+          <t>増収額は平年度ベース</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>5%・10%・15%の3水準。32表ベースの経費回収率が経営戦略のR16目標を</t>
+          <t>施行日が未定のため初年度影響額は含まない。確定後に別途算定が必要</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1231,7 @@
       <c r="A69" s="3" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>既に上回っているため、20%改定は検討対象から外している</t>
+          <t>経費回収率はR6決算の使用料・汚水処理費を固定した静態試算の参考値</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1242,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>案A／案Bの違い</t>
+          <t>検討する改定率</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>案A＝全区分の単価を一律に引き上げる（体系は変えない）</t>
+          <t>5%・10%・15%の3水準。32表ベースの経費回収率が経営戦略のR16目標を</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1255,23 @@
       <c r="A72" s="3" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>案B＝基本使用料は据置（少量利用者への配慮）／6〜10㎥の割安単価を是正／</t>
+          <t>既に上回っているため、20%改定は検討対象から外している</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　51㎥〜（大口）は全体改定率と同水準にとどめる。区分の数は現行のまま</t>
-        </is>
-      </c>
+      <c r="B73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>案A／案Bの違い</t>
+        </is>
+      </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>同じ改定率なら増収額・経費回収率はほぼ同一。違いは負担の分布だけに現れる</t>
+          <t>案A＝全区分の単価を一律に引き上げる（体系は変えない）</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1279,7 @@
       <c r="A75" s="3" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>案Bは月5㎥以下が据置となる分、それ以外の層が全体率より2〜3ポイント高くなる</t>
+          <t>案B＝基本使用料は据置（少量利用者への配慮）／6〜10㎥の割安単価を是正／</t>
         </is>
       </c>
     </row>
@@ -1272,23 +1287,23 @@
       <c r="A76" s="3" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>大口は件数1%前後（公共0.8%・漁集1.5%）で、両案とも負担増は全体率とほぼ同じ</t>
+          <t xml:space="preserve">　　　51㎥〜（大口）は全体改定率と同水準にとどめる。区分の数は現行のまま</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>同じ改定率なら増収額・経費回収率はほぼ同一。違いは負担の分布だけに現れる</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>現行使用料の算定式</t>
-        </is>
-      </c>
+      <c r="A78" s="3" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>隔月検針のため1請求＝2か月分。2か月水量Vに対し区分境界を2倍(10/20/100㎥)して適用</t>
+          <t>案Bは月5㎥以下が据置となる分、それ以外の層が全体率より2〜3ポイント高くなる</t>
         </is>
       </c>
     </row>
@@ -1296,39 +1311,39 @@
       <c r="A79" s="3" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2か月分請求額（税込） = FLOOR( 税抜額 × 1.1 )</t>
+          <t>大口は件数1%前後（公共0.8%・漁集1.5%）で、両案とも負担増は全体率とほぼ同じ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>税抜額 = 2,016 ＋ 37×(V−10)[10&lt;V≦20] ＋ 174×(V−20)[20&lt;V≦100] ＋ 200×(V−100)[100&lt;V]</t>
-        </is>
-      </c>
+      <c r="B80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>現行使用料の算定式</t>
+        </is>
+      </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>R8.3月調定1,519件のうち1,428件（94.0%）がこの式と完全一致（シート06）</t>
+          <t>隔月検針のため1請求＝2か月分。2か月水量Vに対し区分境界を2倍(10/20/100㎥)して適用</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2か月分請求額（税込） = FLOOR( 税抜額 × 1.1 )</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>調定の3区分</t>
-        </is>
-      </c>
+      <c r="A83" s="3" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>通常算定＝金額から水量が一意に定まる（2か月11㎥以上）</t>
+          <t>税抜額 = 2,016 ＋ 37×(V−10)[10&lt;V≦20] ＋ 174×(V−20)[20&lt;V≦100] ＋ 200×(V−100)[100&lt;V]</t>
         </is>
       </c>
     </row>
@@ -1336,31 +1351,31 @@
       <c r="A84" s="3" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>基本料金帯＝2,217円。2か月1〜10㎥のいずれでも同額のため水量不詳（下限1㎥／上限10㎥）</t>
+          <t>R8.3月調定1,519件のうち1,428件（94.0%）がこの式と完全一致（シート06）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>特殊算定＝日割・月中異動等で料金式に一致しない。水量推計は対象外、増収試算は現行×改定率</t>
-        </is>
-      </c>
+      <c r="B85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr"/>
-      <c r="B86" s="2" t="inlineStr"/>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>調定の3区分</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>通常算定＝金額から水量が一意に定まる（2か月11㎥以上）</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>v2での主な訂正</t>
-        </is>
-      </c>
+      <c r="A87" s="3" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>基本料金帯を1㎥として集計していた誤りを修正（漁集285件・公共1,657件、幅は最大17,478㎥）</t>
+          <t>基本料金帯＝2,217円。2か月1〜10㎥のいずれでも同額のため水量不詳（下限1㎥／上限10㎥）</t>
         </is>
       </c>
     </row>
@@ -1368,31 +1383,31 @@
       <c r="A88" s="3" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>増収試算への影響は軽微。2か月10㎥以下は基本料金のみで金額が決まるため水量に依存しない</t>
+          <t>特殊算定＝日割・月中異動等で料金式に一致しない。水量推計は対象外、増収試算は現行×改定率</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr"/>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>特殊算定の扱い変更による差は2事業計 +4,019円（増収額の0.09%）</t>
-        </is>
-      </c>
+      <c r="B89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr"/>
-      <c r="B90" s="2" t="inlineStr"/>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>v2での主な訂正</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>基本料金帯を1㎥として集計していた誤りを修正（漁集285件・公共1,657件、幅は最大17,478㎥）</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>案1の端数処理</t>
-        </is>
-      </c>
+      <c r="A91" s="3" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>集計ブックの案1集計値 8,218,319円（+11.45%）は奇数㎥を2㎥ブロックに切り上げているため過大。</t>
+          <t>増収試算への影響は軽微。2か月10㎥以下は基本料金のみで金額が決まるため水量に依存しない</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1415,7 @@
       <c r="A92" s="3" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>現行と同じ算定方法で再計算すると 8,136,688円（+10.35%）。本ブックは後者を採用。</t>
+          <t>特殊算定の扱い変更による差は2事業計 +4,019円（増収額の0.09%）</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1426,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>既知の限界</t>
+          <t>案1の端数処理</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>① 集計ブックは奇数月6回分のみ対象。偶数月の調定（漁集で7件・43,091円）が未計上</t>
+          <t>集計ブックの案1集計値 8,218,319円（+11.45%）は奇数㎥を2㎥ブロックに切り上げているため過大。</t>
         </is>
       </c>
     </row>
@@ -1424,29 +1439,53 @@
       <c r="A95" s="3" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>② 毎月検針の大口分は年12回のうち奇数月6回しか捕捉できていない。増収額は過小の可能性</t>
+          <t>現行と同じ算定方法で再計算すると 8,136,688円（+10.35%）。本ブックは後者を採用。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>③ 公共下水道の月別明細は3月分のみ入手済み。他は金額からの逆算</t>
-        </is>
-      </c>
+      <c r="B96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr"/>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>既知の限界</t>
+        </is>
+      </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>④ 漁集2ブック間で1月分に1件差異（オリジナル側に3,800円が1件多い）。本試算は236件側に準拠</t>
+          <t>① 集計ブックは奇数月6回分のみ対象。偶数月の調定（漁集で7件・43,091円）が未計上</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>② 毎月検針の大口分は年12回のうち奇数月6回しか捕捉できていない。増収額は過小の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>③ 公共下水道の月別明細は3月分のみ入手済み。他は金額からの逆算</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>④ 漁集2ブック間で1月分に1件差異（オリジナル側に3,800円が1件多い）。本試算は236件側に準拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>⑤ 特殊算定492件（3,045,941円＝全体の7.1%）は現行×改定率の簡便法によっている</t>
         </is>
@@ -15253,6 +15292,1983 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>基本使用料を改定する場合の試算。令和7年度 年間全件9,220レコード・44,567,510円が基礎</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>日割502件は基本使用料の日数按分であるため、基本使用料の改定率に連動する（A案・B案では基本使用料据置のため不変だった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>異動等96件は水量不明のため平均改定率で連動（不動点反復）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>【1】基本使用料のみを改定（6〜10㎥37円・11〜50㎥174円・51㎥〜200円は据置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>基本使用料(税抜)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>改定率</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>月5㎥の2か月請求額(税込)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>同 増減率</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>平年度増収額(税込)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>平均増収率</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>経費回収率</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>負担が減るレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2327</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>1012653</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>+2.27%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>2439</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>2045107</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>+4.59%</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>51.8%</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>2549</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>3057760</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>+6.86%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>+19.9%</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>2659</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+19.9%</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>4070413</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>+9.13%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>54.0%</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>1228</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>+21.8%</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>2701</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>+21.8%</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>4455674</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>+10.00%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>54.4%</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>感度：基本使用料を税抜100円引き上げると 増収 約2,025千円・平均増収率 +4.54ポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>基本使用料だけで平均増収率+10%を得るには1,228円（+21.8%）が必要。月5㎥の2か月請求額は2,217円→2,701円</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>【2】平均増収率を約10%に固定し、基本使用料の改定率を変える（6〜10㎥＝73円・51㎥〜＝220円に固定し11〜50㎥を逆算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>基本使用料(税抜)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>6〜10㎥</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>11〜50㎥</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>51㎥〜</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>単価の開き</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>平年度増収額(税込)</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>平均増収率</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>経費回収率</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>月5㎥</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>月8㎥</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>月10㎥</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>月15㎥</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>月20㎥</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>月30㎥</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>月50㎥</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>月100㎥</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>191</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>2.62倍</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>4478920</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>+15.1%</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>+12.8%</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>+11.9%</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>+11.1%</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>+10.5%</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>+10.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>2.47倍</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>4414533</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>+9.91%</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>54.4%</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>+19.3%</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>+12.6%</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>+9.9%</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>+7.5%</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>2.33倍</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>4467578</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>+18.7%</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>+23.6%</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>+12.6%</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>+4.3%</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>+1.5%</t>
+        </is>
+      </c>
+      <c r="P21" s="9" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>2.19倍</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>4501679</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>+10.10%</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>+23.2%</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>+27.7%</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>+12.6%</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>+6.5%</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>料金区分を変える場合の試算。いずれも平均増収率が約10%になるよう単価を逆算している</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>B-6（基本水量の廃止）は基本水量内1,934レコードの実水量を特定できないため、想定水量2.5㎥での値。幅は37_に示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>B-5（基本水量10㎥）は日割の対象範囲も広がるため、調定明細での確認が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>案</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>構成（基本使用料/基本水量/従量単価）</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>平年度増収額(税込)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>平均増収率</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>経費回収率</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>単価の開き</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>負担が減るレコード</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>据置レコード</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>増えるレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>B案（現行4区分・基準）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 5㎥ / 73・191・220円</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>4478920</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>+10.05%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>2.62倍</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>2436</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>B-1 3区分化（6〜10㎥を統合）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 5㎥ / 144・220円</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>4502366</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+10.10%</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>—（統合）</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>574</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>2436</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>B-2 第1境界を10㎥→20㎥</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 5㎥ / 133・191・220円</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>4505627</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1.44倍</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>2436</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>B-3 上位境界を50㎥→100㎥</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 5㎥ / 73・193・220円</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>4505699</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>+10.11%</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>2.64倍</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>2436</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>B-4 大口区分の新設（100㎥超）</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 5㎥ / 73・184・220・260円</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>4488153</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>+10.07%</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>3.01倍</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>2436</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>6784</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>B-5 基本水量を5㎥→10㎥</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>1,200円 / 10㎥ / 200・220円</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>4500246</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+10.10%</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>—（統合）</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>9220</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>B-6 基本水量の廃止（1㎥目から課金）</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>1,008円 / 0㎥ / 31・191・220円</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>4466073</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>6.16倍</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>502</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>8718</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>【使用量別の2か月請求額（税込）と現行比増減率】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>案</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>月5㎥</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>月8㎥</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>月10㎥</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>月15㎥</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>月20㎥</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>月30㎥</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>月50㎥</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>月100㎥</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>B案（現行4区分・基準）</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>2699</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>+15.1%</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>5121</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>+12.8%</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>7222</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>+11.9%</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>11424</v>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>+11.1%</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>19828</v>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>+10.5%</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>44028</v>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>+10.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>B-1 3区分化（6〜10㎥を統合）</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>3168</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>+28.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>3801</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>+44.9%</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>5385</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>+18.7%</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>6969</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>+8.0%</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>10137</v>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>16473</v>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>-8.2%</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>40673</v>
+      </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>B-2 第1境界を10㎥→20㎥</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>3095</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>+25.8%</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3680</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>+40.2%</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>5143</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>+13.3%</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>6606</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>10808</v>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>+5.1%</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>19212</v>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>43412</v>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>+8.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>B-3 上位境界を50㎥→100㎥</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>2699</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+15.1%</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>5143</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>+13.3%</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>7266</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>+12.6%</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>11512</v>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>+12.0%</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>20004</v>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>+11.5%</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>41234</v>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>B-4 大口区分の新設（100㎥超）</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>2217</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>2699</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>3020</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>+15.1%</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>5044</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>7068</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>+9.5%</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>11116</v>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>19212</v>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>43412</v>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>+8.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>B-5 基本水量を5㎥→10㎥</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>2640</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>+19.1%</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>2640</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>+7.3%</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>4840</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>7040</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>+9.1%</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>11440</v>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>+11.3%</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>20240</v>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>+12.8%</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>44440</v>
+      </c>
+      <c r="Q21" s="9" t="inlineStr">
+        <is>
+          <t>+11.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>B-6 基本水量の廃止（1㎥目から課金）</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>2558</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>+15.4%</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>2763</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>+12.3%</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>2899</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>+10.5%</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>+10.2%</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>7101</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>+10.1%</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>11303</v>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>19707</v>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>+9.9%</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>43907</v>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>+9.9%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>基本水量を現行5㎥より下げる場合、基本水量内1,934レコード（2か月2,217円）の実水量は</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>1〜10㎥（月あたり0〜5㎥）のいずれでも同額のため、集計ブックからは特定できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>したがって想定水量を置くほかなく、0㎥（下限）〜5㎥（上限）で幅を示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>料金表</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>想定水量</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>平年度増収額(税込)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>平均増収率</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>経費回収率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>基本504円 + 1〜10㎥ 98円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>0.0㎥</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>3407356</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>+7.65%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>基本504円 + 1〜10㎥ 98円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2.5㎥</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>4498801</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+10.09%</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>基本504円 + 1〜10㎥ 98円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>5.0㎥</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>5590247</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>+12.54%</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>55.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>基本672円 + 1〜10㎥ 75円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>0.0㎥</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>3550495</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>+7.97%</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>基本672円 + 1〜10㎥ 75円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>2.5㎥</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>4384772</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>+9.84%</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>54.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>基本672円 + 1〜10㎥ 75円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>5.0㎥</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>5221075</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+11.71%</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>55.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>基本1008円 + 1〜10㎥ 31円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>0.0㎥</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>4119807</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>+9.24%</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>54.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>基本1008円 + 1〜10㎥ 31円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>2.5㎥</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>4466073</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>+10.02%</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>基本1008円 + 1〜10㎥ 31円 / 11〜50㎥ 191円 / 51㎥〜 220円</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>5.0㎥</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>4810313</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>+10.79%</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>基本使用料を据え置くほど幅は狭くなる（基本1,008円では +9.24〜+10.79%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>基本使用料を下げるほど従量単価への依存が増し、想定水量の影響を強く受ける。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
